--- a/experiments/nrp_sat_bdd_exp_results.xlsx
+++ b/experiments/nrp_sat_bdd_exp_results.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,30 +447,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>encoding_time_sec</t>
+          <t>total_time_sec</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>solving_time_sec</t>
+          <t>peak_memory_mb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total_time_sec</t>
+          <t>total_clauses</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>peak_memory_mb</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>total_clauses</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>total_variables</t>
         </is>
@@ -495,19 +485,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0476336</v>
+        <v>0.0509405</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0033069</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.0509405</v>
-      </c>
-      <c r="I2" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -528,19 +512,13 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0464272</v>
+        <v>0.04914</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00271281</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.04914</v>
-      </c>
-      <c r="I3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -561,19 +539,13 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0459506</v>
+        <v>0.0486469</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0026963</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0486469</v>
-      </c>
-      <c r="I4" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -594,19 +566,13 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0467455</v>
+        <v>0.0499719</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0032264</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0499719</v>
-      </c>
-      <c r="I5" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -627,19 +593,13 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0468162</v>
+        <v>0.049562</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00274581</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.049562</v>
-      </c>
-      <c r="I6" t="n">
         <v>8.5</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -660,19 +620,13 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0460983</v>
+        <v>0.0484759</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00237766</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.0484759</v>
-      </c>
-      <c r="I7" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -693,19 +647,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0479079</v>
+        <v>0.0509525</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00304461</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.0509525</v>
-      </c>
-      <c r="I8" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -726,19 +674,13 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.048095</v>
+        <v>0.050639</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00254395</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.050639</v>
-      </c>
-      <c r="I9" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -759,19 +701,13 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0455709</v>
+        <v>0.0479398</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00236888</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.0479398</v>
-      </c>
-      <c r="I10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -792,19 +728,13 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0456859</v>
+        <v>0.048268</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0025821</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.048268</v>
-      </c>
-      <c r="I11" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -827,19 +757,13 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.04669311</v>
+        <v>0.04945365</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002760542</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.04945365</v>
-      </c>
-      <c r="I12" t="n">
         <v>8.9</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -852,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,30 +807,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>encoding_time_sec</t>
+          <t>total_time_sec</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>solving_time_sec</t>
+          <t>peak_memory_mb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total_time_sec</t>
+          <t>total_clauses</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>peak_memory_mb</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>total_clauses</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>total_variables</t>
         </is>
@@ -931,19 +845,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0890898</v>
+        <v>0.0949255</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00583576</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.0949255</v>
-      </c>
-      <c r="I2" t="n">
         <v>15.7</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -964,19 +872,13 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0885563</v>
+        <v>0.0936823</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0051259</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.0936823</v>
-      </c>
-      <c r="I3" t="n">
         <v>15.7</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,19 +899,13 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0871721</v>
+        <v>0.0911739</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00400175</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0911739</v>
-      </c>
-      <c r="I4" t="n">
         <v>14.5</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1030,19 +926,13 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09026240000000001</v>
+        <v>0.0959313</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00566894</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0959313</v>
-      </c>
-      <c r="I5" t="n">
         <v>15.1</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1063,19 +953,13 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09051720000000001</v>
+        <v>0.0957291</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00521189</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.0957291</v>
-      </c>
-      <c r="I6" t="n">
         <v>15</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1096,19 +980,13 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0866788</v>
+        <v>0.09075660000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00407781</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.09075660000000001</v>
-      </c>
-      <c r="I7" t="n">
         <v>14.5</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1129,19 +1007,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08821420000000001</v>
+        <v>0.0927148</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00450065</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.0927148</v>
-      </c>
-      <c r="I8" t="n">
         <v>15.7</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1162,19 +1034,13 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0911633</v>
+        <v>0.0975178</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00635459</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0975178</v>
-      </c>
-      <c r="I9" t="n">
         <v>15</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1195,19 +1061,13 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0892155</v>
+        <v>0.0947707</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0055552</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.0947707</v>
-      </c>
-      <c r="I10" t="n">
         <v>15.1</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1228,19 +1088,13 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0873261</v>
+        <v>0.0913339</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00400778</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.0913339</v>
-      </c>
-      <c r="I11" t="n">
         <v>15.7</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1263,19 +1117,13 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08881957</v>
+        <v>0.09385359</v>
       </c>
       <c r="G12" t="n">
-        <v>0.005034027000000001</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.09385359</v>
-      </c>
-      <c r="I12" t="n">
         <v>15.2</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1288,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1319,30 +1167,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>encoding_time_sec</t>
+          <t>total_time_sec</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>solving_time_sec</t>
+          <t>peak_memory_mb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total_time_sec</t>
+          <t>total_clauses</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>peak_memory_mb</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>total_clauses</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>total_variables</t>
         </is>
@@ -1367,19 +1205,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.132824</v>
+        <v>0.140727</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007902299999999999</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.140727</v>
-      </c>
-      <c r="I2" t="n">
         <v>22.1</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1400,19 +1232,13 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.134056</v>
+        <v>0.141943</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00788706</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.141943</v>
-      </c>
-      <c r="I3" t="n">
         <v>22.1</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1433,19 +1259,13 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.138109</v>
+        <v>0.146315</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008206130000000001</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.146315</v>
-      </c>
-      <c r="I4" t="n">
         <v>23.2</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1466,19 +1286,13 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.132919</v>
+        <v>0.13992</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00700027</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.13992</v>
-      </c>
-      <c r="I5" t="n">
         <v>22.4</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1499,19 +1313,13 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.136478</v>
+        <v>0.144834</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008356199999999999</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.144834</v>
-      </c>
-      <c r="I6" t="n">
         <v>23.6</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1532,19 +1340,13 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.144364</v>
+        <v>0.152934</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00856986</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.152934</v>
-      </c>
-      <c r="I7" t="n">
         <v>23.6</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1565,19 +1367,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.139338</v>
+        <v>0.148417</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009078650000000001</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.148417</v>
-      </c>
-      <c r="I8" t="n">
         <v>23.3</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1598,19 +1394,13 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.137298</v>
+        <v>0.14504</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00774202</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.14504</v>
-      </c>
-      <c r="I9" t="n">
         <v>23.6</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1631,19 +1421,13 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.138809</v>
+        <v>0.146819</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00800993</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.146819</v>
-      </c>
-      <c r="I10" t="n">
         <v>23.3</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1664,19 +1448,13 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.138587</v>
+        <v>0.14679</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00820309</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.14679</v>
-      </c>
-      <c r="I11" t="n">
         <v>23.3</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1699,19 +1477,13 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1372782</v>
+        <v>0.1453739</v>
       </c>
       <c r="G12" t="n">
-        <v>0.008095550999999999</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.1453739</v>
-      </c>
-      <c r="I12" t="n">
         <v>23.05</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1724,7 +1496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1755,30 +1527,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>encoding_time_sec</t>
+          <t>total_time_sec</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>solving_time_sec</t>
+          <t>peak_memory_mb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total_time_sec</t>
+          <t>total_clauses</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>peak_memory_mb</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>total_clauses</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>total_variables</t>
         </is>
@@ -1803,19 +1565,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.174549</v>
+        <v>0.184594</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0100449</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.184594</v>
-      </c>
-      <c r="I2" t="n">
         <v>28</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1836,19 +1592,13 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.173385</v>
+        <v>0.18361</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0102257</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.18361</v>
-      </c>
-      <c r="I3" t="n">
         <v>27.5</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1869,19 +1619,13 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.176883</v>
+        <v>0.187062</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0101787</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.187062</v>
-      </c>
-      <c r="I4" t="n">
         <v>28.6</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1902,19 +1646,13 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.175848</v>
+        <v>0.185224</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009375619999999999</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.185224</v>
-      </c>
-      <c r="I5" t="n">
         <v>28.3</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1935,19 +1673,13 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.17814</v>
+        <v>0.189018</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0108777</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.189018</v>
-      </c>
-      <c r="I6" t="n">
         <v>28</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1968,19 +1700,13 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.175022</v>
+        <v>0.186017</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0109945</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.186017</v>
-      </c>
-      <c r="I7" t="n">
         <v>27.7</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2001,19 +1727,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.177476</v>
+        <v>0.18885</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0113741</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.18885</v>
-      </c>
-      <c r="I8" t="n">
         <v>28</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2034,19 +1754,13 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.181928</v>
+        <v>0.192644</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0107158</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.192644</v>
-      </c>
-      <c r="I9" t="n">
         <v>27.5</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2067,19 +1781,13 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.177871</v>
+        <v>0.188331</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0104599</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.188331</v>
-      </c>
-      <c r="I10" t="n">
         <v>28</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2100,19 +1808,13 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.178217</v>
+        <v>0.189235</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0110176</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.189235</v>
-      </c>
-      <c r="I11" t="n">
         <v>28.2</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2135,19 +1837,13 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1769319</v>
+        <v>0.1874585</v>
       </c>
       <c r="G12" t="n">
-        <v>0.010526452</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.1874585</v>
-      </c>
-      <c r="I12" t="n">
         <v>27.98</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
